--- a/jogos_2026-02-14.xlsx
+++ b/jogos_2026-02-14.xlsx
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46067.125</v>
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46067.23263888889</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46067.3125</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2096,64 +2096,64 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46067.3125</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.55</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.86</v>
+        <v>4.62</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46067.35416666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="M26" t="n">
-        <v>2.83</v>
+        <v>3.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46067.35416666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.39</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46067.41666666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="M47" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>3.09</v>
+        <v>3.73</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sangiuliano City</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lentigione</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Imolese</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Progresso</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sangiuliano City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Lentigione</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Imolese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Progresso</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.54</v>
+        <v>8.5</v>
       </c>
       <c r="M76" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="N76" t="n">
-        <v>5.89</v>
+        <v>1.28</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46067.45833333334</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>4.11</v>
+        <v>5.53</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gozzano</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46067.45833333334</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Gozzano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>9</v>
+        <v>1.22</v>
       </c>
       <c r="M83" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="N83" t="n">
-        <v>1.33</v>
+        <v>10.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>8.99</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>10.3</v>
+        <v>4.11</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8.99</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,73 +10893,73 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N88" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="O88" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>46067.45833333334</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.28</v>
+        <v>12.4</v>
       </c>
       <c r="M91" t="n">
-        <v>3.86</v>
+        <v>6.24</v>
       </c>
       <c r="N91" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,16 +11295,16 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>12.4</v>
+        <v>2.28</v>
       </c>
       <c r="M93" t="n">
-        <v>6.24</v>
+        <v>3.86</v>
       </c>
       <c r="N93" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,16 +11533,16 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.4</v>
+        <v>5.02</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N95" t="n">
-        <v>2.68</v>
+        <v>1.61</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.34</v>
+        <v>4.23</v>
       </c>
       <c r="M98" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="N98" t="n">
-        <v>6.87</v>
+        <v>1.74</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O100" t="n">
+        <v>4</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S100" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T100" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V100" t="n">
+        <v>8</v>
+      </c>
+      <c r="W100" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA100" t="n">
         <v>2.05</v>
       </c>
-      <c r="M100" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N100" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>0</v>
-      </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46067.5</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12555,77 +12555,77 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="M102" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N102" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="O102" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P102" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T102" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V102" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W102" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC102" t="n">
         <v>3.5</v>
       </c>
-      <c r="N102" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI102" s="3" t="n">
         <v>46067.5</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.77</v>
+        <v>2.14</v>
       </c>
       <c r="M105" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="N105" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="M106" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>3.13</v>
+        <v>2.63</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,73 +13273,73 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI108" s="3" t="n">
         <v>46067.5</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="M110" t="n">
-        <v>3.1</v>
+        <v>3.49</v>
       </c>
       <c r="N110" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.49</v>
+        <v>3.26</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="N111" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>4.23</v>
+        <v>2.4</v>
       </c>
       <c r="M112" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>1.74</v>
+        <v>2.68</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="M113" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="N113" t="n">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="M114" t="n">
-        <v>13.7</v>
+        <v>4.75</v>
       </c>
       <c r="N114" t="n">
-        <v>38</v>
+        <v>6.87</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="M115" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N115" t="n">
-        <v>7.2</v>
+        <v>3.14</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.88</v>
+        <v>2.77</v>
       </c>
       <c r="M117" t="n">
-        <v>3.64</v>
+        <v>2.94</v>
       </c>
       <c r="N117" t="n">
-        <v>3.83</v>
+        <v>2.69</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="M118" t="n">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M119" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="N119" t="n">
-        <v>6.94</v>
+        <v>7.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="M121" t="n">
-        <v>4.1</v>
+        <v>4.44</v>
       </c>
       <c r="N121" t="n">
-        <v>4.89</v>
+        <v>6.94</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.4</v>
+        <v>5.41</v>
       </c>
       <c r="M122" t="n">
-        <v>3.13</v>
+        <v>3.9</v>
       </c>
       <c r="N122" t="n">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="M125" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N125" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="M126" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="N126" t="n">
-        <v>3.81</v>
+        <v>2.68</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.39</v>
+        <v>1.77</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="N127" t="n">
-        <v>2.87</v>
+        <v>4.12</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15649,77 +15649,77 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.85</v>
+        <v>9.25</v>
       </c>
       <c r="M128" t="n">
-        <v>3.31</v>
+        <v>4.35</v>
       </c>
       <c r="N128" t="n">
-        <v>4.04</v>
+        <v>1.37</v>
       </c>
       <c r="O128" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X128" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC128" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
         <v>46067.5</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="M129" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="N129" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N132" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>5.41</v>
+        <v>2.1</v>
       </c>
       <c r="M133" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N133" t="n">
-        <v>1.54</v>
+        <v>3.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="M136" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N136" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>9.25</v>
+        <v>1.91</v>
       </c>
       <c r="M137" t="n">
-        <v>4.35</v>
+        <v>3.45</v>
       </c>
       <c r="N137" t="n">
-        <v>1.37</v>
+        <v>3.81</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,73 +16843,73 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="M138" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="N138" t="n">
-        <v>4.12</v>
+        <v>4.75</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W138" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD138" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG138" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI138" s="3" t="n">
         <v>46067.5</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M140" t="n">
         <v>3.2</v>
       </c>
-      <c r="M140" t="n">
-        <v>3.11</v>
-      </c>
       <c r="N140" t="n">
-        <v>2.37</v>
+        <v>3.86</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="M141" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N141" t="n">
-        <v>3.86</v>
+        <v>2.37</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,73 +17557,73 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC144" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG144" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH144" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI144" s="3" t="n">
         <v>46067.52083333334</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.07</v>
+        <v>3.09</v>
       </c>
       <c r="M145" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N145" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.87</v>
+        <v>3.06</v>
       </c>
       <c r="M150" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N150" t="n">
-        <v>4.21</v>
+        <v>2.27</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="M156" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N156" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="M157" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="N157" t="n">
-        <v>2.41</v>
+        <v>5.01</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="M159" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N159" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="M160" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N160" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.74</v>
+        <v>4.03</v>
       </c>
       <c r="M162" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N162" t="n">
-        <v>4.19</v>
+        <v>1.86</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="M164" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="N164" t="n">
-        <v>5.01</v>
+        <v>2.41</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="N172" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="M178" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N178" t="n">
-        <v>7.01</v>
+        <v>2.33</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22368,10 +22368,10 @@
         <v>0</v>
       </c>
       <c r="AC184" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD184" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>9.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="M185" t="n">
-        <v>5.5</v>
+        <v>3.29</v>
       </c>
       <c r="N185" t="n">
-        <v>1.28</v>
+        <v>3.19</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.58</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M186" t="n">
-        <v>4.62</v>
+        <v>5.5</v>
       </c>
       <c r="N186" t="n">
-        <v>6.09</v>
+        <v>1.28</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22606,10 +22606,10 @@
         <v>0</v>
       </c>
       <c r="AC186" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD186" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3.52</v>
+        <v>2.22</v>
       </c>
       <c r="M192" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N192" t="n">
-        <v>2.1</v>
+        <v>3.02</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.22</v>
+        <v>3.52</v>
       </c>
       <c r="M193" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N193" t="n">
-        <v>3.02</v>
+        <v>2.1</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.37</v>
+        <v>3.22</v>
       </c>
       <c r="M196" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N196" t="n">
-        <v>2.77</v>
+        <v>2.11</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="M197" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N197" t="n">
-        <v>3.59</v>
+        <v>4.28</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="M198" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N198" t="n">
-        <v>4.28</v>
+        <v>2.77</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>3.22</v>
+        <v>1.89</v>
       </c>
       <c r="M199" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N199" t="n">
-        <v>2.11</v>
+        <v>3.59</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.53</v>
+        <v>1.45</v>
       </c>
       <c r="M200" t="n">
-        <v>3.62</v>
+        <v>4.69</v>
       </c>
       <c r="N200" t="n">
-        <v>2.5</v>
+        <v>7.15</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="M201" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N201" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,10 +24459,10 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="M202" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="N202" t="n">
         <v>2.5</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="M204" t="n">
-        <v>4.69</v>
+        <v>3.28</v>
       </c>
       <c r="N204" t="n">
-        <v>7.15</v>
+        <v>3.32</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>4.33</v>
+        <v>2.08</v>
       </c>
       <c r="M208" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N208" t="n">
-        <v>1.92</v>
+        <v>3.97</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.09</v>
+        <v>4.33</v>
       </c>
       <c r="M209" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="N209" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.08</v>
+        <v>3.09</v>
       </c>
       <c r="M210" t="n">
-        <v>3.54</v>
+        <v>3.22</v>
       </c>
       <c r="N210" t="n">
-        <v>3.97</v>
+        <v>2.31</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="M211" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="N211" t="n">
-        <v>3.71</v>
+        <v>3.05</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="M212" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="N212" t="n">
-        <v>3.73</v>
+        <v>4.31</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25688,16 +25688,16 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,22 +25851,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="M215" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="N215" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26045,10 +26045,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -26089,22 +26089,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="M216" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="N216" t="n">
-        <v>3.05</v>
+        <v>3.73</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L224" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L226" t="n">
